--- a/docs/downloads/20260924_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260924_Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AV21"/>
+  <dimension ref="A2:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,10 @@
     <col width="9" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
-    <col width="46" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+    <col width="46" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -599,8 +602,11 @@
       <c r="AP3" s="3" t="n">
         <v>46276</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AS3" s="3" t="n">
         <v>46283</v>
+      </c>
+      <c r="AV3" s="4" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -826,22 +832,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AS4" s="6" t="inlineStr">
+      <c r="AS4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AT4" s="6" t="inlineStr">
+      <c r="AT4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AU4" s="6" t="inlineStr">
+      <c r="AU4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AV4" s="5" t="inlineStr">
+      <c r="AV4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AW4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AX4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -900,6 +921,9 @@
       <c r="AT5" s="8" t="n"/>
       <c r="AU5" s="8" t="n"/>
       <c r="AV5" s="8" t="n"/>
+      <c r="AW5" s="8" t="n"/>
+      <c r="AX5" s="8" t="n"/>
+      <c r="AY5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1061,20 +1085,31 @@
         <f>AQ6/$D$6</f>
         <v/>
       </c>
-      <c r="AS6" s="14">
+      <c r="AS6" s="12">
         <f>AT6-AQ6</f>
         <v/>
       </c>
-      <c r="AT6" s="14" t="n">
+      <c r="AT6" s="12" t="n">
         <v>317</v>
       </c>
-      <c r="AU6" s="15">
+      <c r="AU6" s="13">
         <f>AT6/$D$6</f>
         <v/>
       </c>
-      <c r="AV6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 194 units, Block B: 123 units</t>
+      <c r="AV6" s="14">
+        <f>AW6-AT6</f>
+        <v/>
+      </c>
+      <c r="AW6" s="14" t="n">
+        <v>321</v>
+      </c>
+      <c r="AX6" s="15">
+        <f>AW6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 195 units, Block B: 126 units</t>
         </is>
       </c>
     </row>
@@ -1238,20 +1273,31 @@
         <f>AQ7/$D$7</f>
         <v/>
       </c>
-      <c r="AS7" s="14">
+      <c r="AS7" s="12">
         <f>AT7-AQ7</f>
         <v/>
       </c>
-      <c r="AT7" s="14" t="n">
+      <c r="AT7" s="12" t="n">
         <v>993</v>
       </c>
-      <c r="AU7" s="15">
+      <c r="AU7" s="13">
         <f>AT7/$D$7</f>
         <v/>
       </c>
-      <c r="AV7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 409 units, Block B: 386 units, Block C: 89 units, Block D: 109 units</t>
+      <c r="AV7" s="14">
+        <f>AW7-AT7</f>
+        <v/>
+      </c>
+      <c r="AW7" s="14" t="n">
+        <v>1007</v>
+      </c>
+      <c r="AX7" s="15">
+        <f>AW7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 415 units, Block B: 391 units, Block C: 91 units, Block D: 110 units</t>
         </is>
       </c>
     </row>
@@ -1415,18 +1461,29 @@
         <f>AQ8/$D$8</f>
         <v/>
       </c>
-      <c r="AS8" s="14">
+      <c r="AS8" s="12">
         <f>AT8-AQ8</f>
         <v/>
       </c>
-      <c r="AT8" s="14" t="n">
+      <c r="AT8" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="AU8" s="15">
+      <c r="AU8" s="13">
         <f>AT8/$D$8</f>
         <v/>
       </c>
-      <c r="AV8" s="10" t="inlineStr">
+      <c r="AV8" s="14">
+        <f>AW8-AT8</f>
+        <v/>
+      </c>
+      <c r="AW8" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="AX8" s="15">
+        <f>AW8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1592,20 +1649,31 @@
         <f>AQ9/$D$9</f>
         <v/>
       </c>
-      <c r="AS9" s="14">
+      <c r="AS9" s="12">
         <f>AT9-AQ9</f>
         <v/>
       </c>
-      <c r="AT9" s="14" t="n">
+      <c r="AT9" s="12" t="n">
         <v>1076</v>
       </c>
-      <c r="AU9" s="15">
+      <c r="AU9" s="13">
         <f>AT9/$D$9</f>
         <v/>
       </c>
-      <c r="AV9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 670 units, Phase 2: 406 units</t>
+      <c r="AV9" s="14">
+        <f>AW9-AT9</f>
+        <v/>
+      </c>
+      <c r="AW9" s="14" t="n">
+        <v>1086</v>
+      </c>
+      <c r="AX9" s="15">
+        <f>AW9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 671 units, Phase 2: 415 units</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1730,9 @@
       <c r="AT10" s="8" t="n"/>
       <c r="AU10" s="8" t="n"/>
       <c r="AV10" s="8" t="n"/>
+      <c r="AW10" s="8" t="n"/>
+      <c r="AX10" s="8" t="n"/>
+      <c r="AY10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1823,18 +1894,29 @@
         <f>AQ11/$D$11</f>
         <v/>
       </c>
-      <c r="AS11" s="14">
+      <c r="AS11" s="12">
         <f>AT11-AQ11</f>
         <v/>
       </c>
-      <c r="AT11" s="14" t="n">
+      <c r="AT11" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="AU11" s="15">
+      <c r="AU11" s="13">
         <f>AT11/$D$11</f>
         <v/>
       </c>
-      <c r="AV11" s="10" t="inlineStr">
+      <c r="AV11" s="14">
+        <f>AW11-AT11</f>
+        <v/>
+      </c>
+      <c r="AW11" s="14" t="n">
+        <v>845</v>
+      </c>
+      <c r="AX11" s="15">
+        <f>AW11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2000,20 +2082,31 @@
         <f>AQ12/$D$12</f>
         <v/>
       </c>
-      <c r="AS12" s="14">
+      <c r="AS12" s="12">
         <f>AT12-AQ12</f>
         <v/>
       </c>
-      <c r="AT12" s="14" t="n">
+      <c r="AT12" s="12" t="n">
         <v>1542</v>
       </c>
-      <c r="AU12" s="15">
+      <c r="AU12" s="13">
         <f>AT12/$D$12</f>
         <v/>
       </c>
-      <c r="AV12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 520 units, Block B: 535 units, Block D: 487 units</t>
+      <c r="AV12" s="14">
+        <f>AW12-AT12</f>
+        <v/>
+      </c>
+      <c r="AW12" s="14" t="n">
+        <v>1559</v>
+      </c>
+      <c r="AX12" s="15">
+        <f>AW12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 527 units, Block B: 538 units, Block D: 494 units</t>
         </is>
       </c>
     </row>
@@ -2177,20 +2270,31 @@
         <f>AQ13/$D$13</f>
         <v/>
       </c>
-      <c r="AS13" s="14">
+      <c r="AS13" s="12">
         <f>AT13-AQ13</f>
         <v/>
       </c>
-      <c r="AT13" s="14" t="n">
+      <c r="AT13" s="12" t="n">
         <v>1031</v>
       </c>
-      <c r="AU13" s="15">
+      <c r="AU13" s="13">
         <f>AT13/$D$13</f>
         <v/>
       </c>
-      <c r="AV13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 407 units, Block B: 376 units, Block C: 248 units</t>
+      <c r="AV13" s="14">
+        <f>AW13-AT13</f>
+        <v/>
+      </c>
+      <c r="AW13" s="14" t="n">
+        <v>1045</v>
+      </c>
+      <c r="AX13" s="15">
+        <f>AW13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 408 units, Block B: 380 units, Block C: 257 units</t>
         </is>
       </c>
     </row>
@@ -2354,20 +2458,31 @@
         <f>AQ14/$D$14</f>
         <v/>
       </c>
-      <c r="AS14" s="14">
+      <c r="AS14" s="12">
         <f>AT14-AQ14</f>
         <v/>
       </c>
-      <c r="AT14" s="14" t="n">
+      <c r="AT14" s="12" t="n">
         <v>785</v>
       </c>
-      <c r="AU14" s="15">
+      <c r="AU14" s="13">
         <f>AT14/$D$14</f>
         <v/>
       </c>
-      <c r="AV14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 510 units, Block B: 275 units</t>
+      <c r="AV14" s="14">
+        <f>AW14-AT14</f>
+        <v/>
+      </c>
+      <c r="AW14" s="14" t="n">
+        <v>797</v>
+      </c>
+      <c r="AX14" s="15">
+        <f>AW14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 516 units, Block B: 281 units</t>
         </is>
       </c>
     </row>
@@ -2531,20 +2646,31 @@
         <f>AQ15/$D$15</f>
         <v/>
       </c>
-      <c r="AS15" s="14">
+      <c r="AS15" s="12">
         <f>AT15-AQ15</f>
         <v/>
       </c>
-      <c r="AT15" s="14" t="n">
+      <c r="AT15" s="12" t="n">
         <v>1404</v>
       </c>
-      <c r="AU15" s="15">
+      <c r="AU15" s="13">
         <f>AT15/$D$15</f>
         <v/>
       </c>
-      <c r="AV15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 728 units, Block B: 676 units</t>
+      <c r="AV15" s="14">
+        <f>AW15-AT15</f>
+        <v/>
+      </c>
+      <c r="AW15" s="14" t="n">
+        <v>1409</v>
+      </c>
+      <c r="AX15" s="15">
+        <f>AW15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 731 units, Block B: 678 units</t>
         </is>
       </c>
     </row>
@@ -2708,18 +2834,29 @@
         <f>AQ16/$D$16</f>
         <v/>
       </c>
-      <c r="AS16" s="14">
+      <c r="AS16" s="12">
         <f>AT16-AQ16</f>
         <v/>
       </c>
-      <c r="AT16" s="14" t="n">
+      <c r="AT16" s="12" t="n">
         <v>916</v>
       </c>
-      <c r="AU16" s="15">
+      <c r="AU16" s="13">
         <f>AT16/$D$16</f>
         <v/>
       </c>
-      <c r="AV16" s="10" t="inlineStr">
+      <c r="AV16" s="14">
+        <f>AW16-AT16</f>
+        <v/>
+      </c>
+      <c r="AW16" s="14" t="n">
+        <v>917</v>
+      </c>
+      <c r="AX16" s="15">
+        <f>AW16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2843,10 +2980,13 @@
       <c r="AP17" s="12" t="n"/>
       <c r="AQ17" s="12" t="n"/>
       <c r="AR17" s="13" t="n"/>
-      <c r="AS17" s="14" t="n"/>
-      <c r="AT17" s="14" t="n"/>
-      <c r="AU17" s="15" t="n"/>
-      <c r="AV17" s="10" t="inlineStr">
+      <c r="AS17" s="12" t="n"/>
+      <c r="AT17" s="12" t="n"/>
+      <c r="AU17" s="13" t="n"/>
+      <c r="AV17" s="14" t="n"/>
+      <c r="AW17" s="14" t="n"/>
+      <c r="AX17" s="15" t="n"/>
+      <c r="AY17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -3012,20 +3152,31 @@
         <f>AQ18/$D$18</f>
         <v/>
       </c>
-      <c r="AS18" s="14">
+      <c r="AS18" s="12">
         <f>AT18-AQ18</f>
         <v/>
       </c>
-      <c r="AT18" s="14" t="n">
+      <c r="AT18" s="12" t="n">
         <v>735</v>
       </c>
-      <c r="AU18" s="15">
+      <c r="AU18" s="13">
         <f>AT18/$D$18</f>
         <v/>
       </c>
-      <c r="AV18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 445 units, Block B: 290 units</t>
+      <c r="AV18" s="14">
+        <f>AW18-AT18</f>
+        <v/>
+      </c>
+      <c r="AW18" s="14" t="n">
+        <v>742</v>
+      </c>
+      <c r="AX18" s="15">
+        <f>AW18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AY18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 452 units, Block B: 290 units</t>
         </is>
       </c>
     </row>
@@ -3189,20 +3340,31 @@
         <f>AQ19/$D$19</f>
         <v/>
       </c>
-      <c r="AS19" s="14">
+      <c r="AS19" s="12">
         <f>AT19-AQ19</f>
         <v/>
       </c>
-      <c r="AT19" s="14" t="n">
+      <c r="AT19" s="12" t="n">
         <v>397</v>
       </c>
-      <c r="AU19" s="15">
+      <c r="AU19" s="13">
         <f>AT19/$D$19</f>
         <v/>
       </c>
-      <c r="AV19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 299 units, Block B: 98 units</t>
+      <c r="AV19" s="14">
+        <f>AW19-AT19</f>
+        <v/>
+      </c>
+      <c r="AW19" s="14" t="n">
+        <v>402</v>
+      </c>
+      <c r="AX19" s="15">
+        <f>AW19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AY19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 301 units, Block B: 101 units</t>
         </is>
       </c>
     </row>
@@ -3366,20 +3528,31 @@
         <f>AQ20/$D$20</f>
         <v/>
       </c>
-      <c r="AS20" s="14">
+      <c r="AS20" s="12">
         <f>AT20-AQ20</f>
         <v/>
       </c>
-      <c r="AT20" s="14" t="n">
+      <c r="AT20" s="12" t="n">
         <v>325</v>
       </c>
-      <c r="AU20" s="15">
+      <c r="AU20" s="13">
         <f>AT20/$D$20</f>
         <v/>
       </c>
-      <c r="AV20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 222 units, Block B: 103 units</t>
+      <c r="AV20" s="14">
+        <f>AW20-AT20</f>
+        <v/>
+      </c>
+      <c r="AW20" s="14" t="n">
+        <v>331</v>
+      </c>
+      <c r="AX20" s="15">
+        <f>AW20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AY20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 227 units, Block B: 104 units</t>
         </is>
       </c>
     </row>
@@ -3447,21 +3620,32 @@
         <f>AQ21/$D$21</f>
         <v/>
       </c>
-      <c r="AS21" s="14">
+      <c r="AS21" s="12">
         <f>AT21-AQ21</f>
         <v/>
       </c>
-      <c r="AT21" s="14" t="n">
+      <c r="AT21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" s="15">
+      <c r="AU21" s="13">
         <f>AT21/$D$21</f>
         <v/>
       </c>
-      <c r="AV21" s="10" t="inlineStr"/>
+      <c r="AV21" s="14">
+        <f>AW21-AT21</f>
+        <v/>
+      </c>
+      <c r="AW21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="15">
+        <f>AW21/$D$21</f>
+        <v/>
+      </c>
+      <c r="AY21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>
@@ -3476,6 +3660,7 @@
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AV3:AX3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
